--- a/colleges1.xlsx
+++ b/colleges1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fe091929957c81be/Desktop/college Dashboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nk877\OneDrive\Pictures\Camera Roll\Free show\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{C5929A21-8FEB-42EB-91AD-92EF56DB0BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F39158E-3EE7-4E8B-8169-CB227EC927B8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE48248A-BBC1-4876-A82A-46B5941C30C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E51DEF15-1794-4A01-8E1F-673800EDB52A}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2606" uniqueCount="1094">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3345" uniqueCount="1103">
   <si>
     <t>college_id</t>
   </si>
@@ -3313,6 +3313,33 @@
   </si>
   <si>
     <t>https://kjnec.in/</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Bus Facility</t>
+  </si>
+  <si>
+    <t>Estimated Placement Score</t>
+  </si>
+  <si>
+    <t>Co_Ed</t>
+  </si>
+  <si>
+    <t>Co-ed</t>
+  </si>
+  <si>
+    <t>Women</t>
+  </si>
+  <si>
+    <t>Men</t>
+  </si>
+  <si>
+    <t>UGC_Recognized</t>
   </si>
 </sst>
 </file>
@@ -3810,29 +3837,30 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3893,9 +3921,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3933,7 +3961,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4039,7 +4067,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4181,7 +4209,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4189,25 +4217,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32CF35EF-A036-4518-9862-DA6960BA6B31}">
-  <dimension ref="A1:L246"/>
+  <dimension ref="A1:P246"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="3"/>
-    <col min="2" max="2" width="72" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.77734375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="74.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.5546875" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="45.109375" style="3" customWidth="1"/>
     <col min="7" max="7" width="26" style="3" customWidth="1"/>
     <col min="8" max="8" width="18.77734375" style="3" customWidth="1"/>
     <col min="9" max="9" width="15.6640625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="40.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="66.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="41.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="55.77734375" style="3" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="3"/>
+    <col min="13" max="13" width="10.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="24.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4244,8 +4276,20 @@
       <c r="L1" s="2" t="s">
         <v>1080</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -4261,7 +4305,7 @@
       <c r="E2" s="3" t="s">
         <v>1058</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="G2" s="3" t="s">
@@ -4282,8 +4326,20 @@
       <c r="L2" s="5" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="M2" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N2" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -4320,8 +4376,20 @@
       <c r="L3" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="M3" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N3" s="3">
+        <v>4.3</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -4358,8 +4426,20 @@
       <c r="L4" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="M4" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N4" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -4396,8 +4476,20 @@
       <c r="L5" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="M5" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N5" s="3">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -4434,8 +4526,20 @@
       <c r="L6" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="M6" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N6" s="3">
+        <v>8.4</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -4472,8 +4576,20 @@
       <c r="L7" s="3" t="s">
         <v>1084</v>
       </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="M7" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N7" s="3">
+        <v>6.4</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -4510,8 +4626,20 @@
       <c r="L8" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="M8" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N8" s="3">
+        <v>5</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -4548,8 +4676,20 @@
       <c r="L9" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="M9" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N9" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -4586,8 +4726,20 @@
       <c r="L10" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="M10" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N10" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -4624,8 +4776,20 @@
       <c r="L11" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="M11" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N11" s="3">
+        <v>6.8</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -4662,8 +4826,20 @@
       <c r="L12" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="M12" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N12" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -4700,8 +4876,20 @@
       <c r="L13" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="M13" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N13" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -4738,8 +4926,20 @@
       <c r="L14" s="3" t="s">
         <v>1084</v>
       </c>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="M14" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N14" s="3">
+        <v>7.8</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -4776,8 +4976,20 @@
       <c r="L15" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="M15" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N15" s="3">
+        <v>8.6</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -4814,8 +5026,20 @@
       <c r="L16" s="3" t="s">
         <v>1084</v>
       </c>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="M16" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N16" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -4852,8 +5076,20 @@
       <c r="L17" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="M17" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N17" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -4890,8 +5126,20 @@
       <c r="L18" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="M18" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N18" s="3">
+        <v>5.9</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -4928,8 +5176,20 @@
       <c r="L19" s="3" t="s">
         <v>1084</v>
       </c>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="M19" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N19" s="3">
+        <v>9.6</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -4966,8 +5226,20 @@
       <c r="L20" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="M20" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N20" s="3">
+        <v>9.4</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -5004,8 +5276,20 @@
       <c r="L21" s="3" t="s">
         <v>1084</v>
       </c>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="M21" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N21" s="3">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -5042,8 +5326,20 @@
       <c r="L22" s="3" t="s">
         <v>1084</v>
       </c>
-    </row>
-    <row r="23" spans="1:12">
+      <c r="M22" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N22" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -5080,8 +5376,20 @@
       <c r="L23" s="3" t="s">
         <v>1084</v>
       </c>
-    </row>
-    <row r="24" spans="1:12">
+      <c r="M23" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N23" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -5118,8 +5426,20 @@
       <c r="L24" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="25" spans="1:12">
+      <c r="M24" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N24" s="3">
+        <v>6.3</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -5156,8 +5476,20 @@
       <c r="L25" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="26" spans="1:12">
+      <c r="M25" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N25" s="3">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -5194,8 +5526,20 @@
       <c r="L26" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="27" spans="1:12">
+      <c r="M26" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N26" s="3">
+        <v>4.7</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -5232,8 +5576,20 @@
       <c r="L27" s="3" t="s">
         <v>1084</v>
       </c>
-    </row>
-    <row r="28" spans="1:12">
+      <c r="M27" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N27" s="3">
+        <v>7</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -5270,8 +5626,20 @@
       <c r="L28" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="29" spans="1:12">
+      <c r="M28" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N28" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P28" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -5308,8 +5676,20 @@
       <c r="L29" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="30" spans="1:12">
+      <c r="M29" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N29" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -5346,8 +5726,20 @@
       <c r="L30" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="31" spans="1:12">
+      <c r="M30" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N30" s="3">
+        <v>2.6</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -5384,8 +5776,20 @@
       <c r="L31" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="32" spans="1:12">
+      <c r="M31" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N31" s="3">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -5422,8 +5826,20 @@
       <c r="L32" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="33" spans="1:12">
+      <c r="M32" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N32" s="3">
+        <v>8.5</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -5445,8 +5861,20 @@
       <c r="L33" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="34" spans="1:12">
+      <c r="M33" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N33" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -5483,8 +5911,20 @@
       <c r="L34" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="35" spans="1:12">
+      <c r="M34" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N34" s="3">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -5521,8 +5961,20 @@
       <c r="L35" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="36" spans="1:12">
+      <c r="M35" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N35" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -5559,8 +6011,20 @@
       <c r="L36" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="37" spans="1:12">
+      <c r="M36" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N36" s="3">
+        <v>3.9</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -5597,8 +6061,20 @@
       <c r="L37" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="38" spans="1:12">
+      <c r="M37" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N37" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P37" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -5635,8 +6111,20 @@
       <c r="L38" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="39" spans="1:12">
+      <c r="M38" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N38" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -5673,8 +6161,20 @@
       <c r="L39" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="40" spans="1:12">
+      <c r="M39" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N39" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P39" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -5711,8 +6211,20 @@
       <c r="L40" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="41" spans="1:12">
+      <c r="M40" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N40" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -5749,8 +6261,20 @@
       <c r="L41" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="42" spans="1:12">
+      <c r="M41" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N41" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -5787,8 +6311,20 @@
       <c r="L42" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="43" spans="1:12">
+      <c r="M42" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N42" s="3">
+        <v>7.9</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -5825,8 +6361,20 @@
       <c r="L43" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="44" spans="1:12">
+      <c r="M43" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N43" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -5863,8 +6411,20 @@
       <c r="L44" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="45" spans="1:12">
+      <c r="M44" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N44" s="3">
+        <v>3.7</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -5901,8 +6461,20 @@
       <c r="L45" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="46" spans="1:12">
+      <c r="M45" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N45" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -5939,8 +6511,20 @@
       <c r="L46" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="47" spans="1:12">
+      <c r="M46" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N46" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -5977,8 +6561,20 @@
       <c r="L47" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="48" spans="1:12">
+      <c r="M47" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N47" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -6015,8 +6611,20 @@
       <c r="L48" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="49" spans="1:12">
+      <c r="M48" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N48" s="3">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -6053,8 +6661,20 @@
       <c r="L49" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="50" spans="1:12">
+      <c r="M49" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N49" s="3">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -6091,8 +6711,20 @@
       <c r="L50" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="51" spans="1:12">
+      <c r="M50" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N50" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P50" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -6129,8 +6761,20 @@
       <c r="L51" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="52" spans="1:12">
+      <c r="M51" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N51" s="3">
+        <v>5.3</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P51" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -6167,8 +6811,20 @@
       <c r="L52" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="53" spans="1:12">
+      <c r="M52" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N52" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -6205,8 +6861,20 @@
       <c r="L53" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="54" spans="1:12">
+      <c r="M53" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N53" s="3">
+        <v>5</v>
+      </c>
+      <c r="O53" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P53" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -6243,8 +6911,20 @@
       <c r="L54" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="55" spans="1:12">
+      <c r="M54" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N54" s="3">
+        <v>6.7</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P54" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -6281,8 +6961,20 @@
       <c r="L55" s="3" t="s">
         <v>1084</v>
       </c>
-    </row>
-    <row r="56" spans="1:12">
+      <c r="M55" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N55" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="O55" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="P55" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -6307,8 +6999,20 @@
       <c r="L56" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="57" spans="1:12">
+      <c r="M56" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N56" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P56" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -6345,8 +7049,20 @@
       <c r="L57" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="58" spans="1:12">
+      <c r="M57" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N57" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -6383,8 +7099,20 @@
       <c r="L58" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="59" spans="1:12">
+      <c r="M58" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N58" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -6421,8 +7149,20 @@
       <c r="L59" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="60" spans="1:12">
+      <c r="M59" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N59" s="3">
+        <v>8.6</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -6459,8 +7199,20 @@
       <c r="L60" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="61" spans="1:12">
+      <c r="M60" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N60" s="3">
+        <v>7.4</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P60" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -6497,8 +7249,20 @@
       <c r="L61" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="62" spans="1:12">
+      <c r="M61" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N61" s="3">
+        <v>5.7</v>
+      </c>
+      <c r="O61" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P61" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -6535,8 +7299,20 @@
       <c r="L62" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="63" spans="1:12">
+      <c r="M62" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N62" s="3">
+        <v>5.5</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -6573,8 +7349,20 @@
       <c r="L63" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="64" spans="1:12">
+      <c r="M63" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N63" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="O63" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="P63" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -6611,8 +7399,20 @@
       <c r="L64" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="65" spans="1:12">
+      <c r="M64" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N64" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P64" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -6649,8 +7449,20 @@
       <c r="L65" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="66" spans="1:12">
+      <c r="M65" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N65" s="3">
+        <v>5.3</v>
+      </c>
+      <c r="O65" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P65" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -6687,8 +7499,20 @@
       <c r="L66" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="67" spans="1:12">
+      <c r="M66" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N66" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -6725,8 +7549,20 @@
       <c r="L67" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="68" spans="1:12">
+      <c r="M67" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N67" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="O67" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P67" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -6763,8 +7599,20 @@
       <c r="L68" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="69" spans="1:12">
+      <c r="M68" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N68" s="3">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="O68" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P68" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -6801,8 +7649,20 @@
       <c r="L69" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="70" spans="1:12">
+      <c r="M69" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N69" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="O69" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P69" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -6836,8 +7696,20 @@
       <c r="L70" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="71" spans="1:12">
+      <c r="M70" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N70" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P70" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -6874,8 +7746,20 @@
       <c r="L71" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="72" spans="1:12">
+      <c r="M71" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N71" s="3">
+        <v>4.7</v>
+      </c>
+      <c r="O71" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P71" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16">
       <c r="A72" s="3">
         <v>71</v>
       </c>
@@ -6912,8 +7796,20 @@
       <c r="L72" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="73" spans="1:12">
+      <c r="M72" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N72" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -6950,8 +7846,20 @@
       <c r="L73" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="74" spans="1:12">
+      <c r="M73" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N73" s="3">
+        <v>3.9</v>
+      </c>
+      <c r="O73" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P73" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -6976,8 +7884,20 @@
       <c r="L74" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="75" spans="1:12">
+      <c r="M74" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N74" s="3">
+        <v>5.9</v>
+      </c>
+      <c r="O74" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P74" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -7008,8 +7928,20 @@
       <c r="L75" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="76" spans="1:12">
+      <c r="M75" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N75" s="3">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="O75" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P75" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -7046,8 +7978,20 @@
       <c r="L76" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="77" spans="1:12">
+      <c r="M76" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N76" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P76" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -7084,8 +8028,20 @@
       <c r="L77" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="78" spans="1:12">
+      <c r="M77" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N77" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="O77" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P77" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -7119,8 +8075,20 @@
       <c r="L78" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="79" spans="1:12">
+      <c r="M78" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N78" s="3">
+        <v>3.7</v>
+      </c>
+      <c r="O78" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P78" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -7154,8 +8122,20 @@
       <c r="L79" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="80" spans="1:12">
+      <c r="M79" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N79" s="3">
+        <v>8.6</v>
+      </c>
+      <c r="O79" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P79" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -7192,8 +8172,20 @@
       <c r="L80" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="81" spans="1:12">
+      <c r="M80" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N80" s="3">
+        <v>9.1</v>
+      </c>
+      <c r="O80" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P80" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -7230,8 +8222,20 @@
       <c r="L81" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="82" spans="1:12">
+      <c r="M81" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N81" s="3">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -7268,8 +8272,20 @@
       <c r="L82" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="83" spans="1:12">
+      <c r="M82" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N82" s="3">
+        <v>8.5</v>
+      </c>
+      <c r="O82" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P82" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -7306,8 +8322,20 @@
       <c r="L83" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="84" spans="1:12">
+      <c r="M83" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N83" s="3">
+        <v>6.8</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -7344,8 +8372,20 @@
       <c r="L84" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="85" spans="1:12">
+      <c r="M84" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N84" s="3">
+        <v>8.4</v>
+      </c>
+      <c r="O84" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P84" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -7382,8 +8422,20 @@
       <c r="L85" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="86" spans="1:12">
+      <c r="M85" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N85" s="3">
+        <v>7.8</v>
+      </c>
+      <c r="O85" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P85" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -7420,8 +8472,20 @@
       <c r="L86" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="87" spans="1:12">
+      <c r="M86" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N86" s="3">
+        <v>9.4</v>
+      </c>
+      <c r="O86" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P86" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16">
       <c r="A87" s="3">
         <v>86</v>
       </c>
@@ -7458,8 +8522,20 @@
       <c r="L87" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="88" spans="1:12">
+      <c r="M87" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N87" s="3">
+        <v>7.4</v>
+      </c>
+      <c r="O87" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P87" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16">
       <c r="A88" s="3">
         <v>87</v>
       </c>
@@ -7496,8 +8572,20 @@
       <c r="L88" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="89" spans="1:12">
+      <c r="M88" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N88" s="3">
+        <v>6.9</v>
+      </c>
+      <c r="O88" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P88" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -7534,8 +8622,20 @@
       <c r="L89" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="90" spans="1:12">
+      <c r="M89" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N89" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -7572,8 +8672,20 @@
       <c r="L90" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="91" spans="1:12">
+      <c r="M90" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N90" s="3">
+        <v>7.6</v>
+      </c>
+      <c r="O90" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P90" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16">
       <c r="A91" s="3">
         <v>90</v>
       </c>
@@ -7610,8 +8722,20 @@
       <c r="L91" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="92" spans="1:12">
+      <c r="M91" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N91" s="3">
+        <v>8.9</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16">
       <c r="A92" s="3">
         <v>91</v>
       </c>
@@ -7648,8 +8772,20 @@
       <c r="L92" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="93" spans="1:12">
+      <c r="M92" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N92" s="3">
+        <v>8.6</v>
+      </c>
+      <c r="O92" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P92" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16">
       <c r="A93" s="3">
         <v>92</v>
       </c>
@@ -7686,8 +8822,20 @@
       <c r="L93" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="94" spans="1:12">
+      <c r="M93" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N93" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="O93" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P93" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16">
       <c r="A94" s="3">
         <v>93</v>
       </c>
@@ -7724,8 +8872,20 @@
       <c r="L94" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="95" spans="1:12">
+      <c r="M94" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N94" s="3">
+        <v>7.8</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16">
       <c r="A95" s="3">
         <v>94</v>
       </c>
@@ -7762,8 +8922,20 @@
       <c r="L95" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="96" spans="1:12">
+      <c r="M95" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N95" s="3">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="O95" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P95" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16">
       <c r="A96" s="3">
         <v>95</v>
       </c>
@@ -7800,8 +8972,20 @@
       <c r="L96" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="97" spans="1:12">
+      <c r="M96" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N96" s="3">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -7838,8 +9022,20 @@
       <c r="L97" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="98" spans="1:12">
+      <c r="M97" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N97" s="3">
+        <v>6.9</v>
+      </c>
+      <c r="O97" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P97" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16">
       <c r="A98" s="3">
         <v>97</v>
       </c>
@@ -7876,8 +9072,20 @@
       <c r="L98" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="99" spans="1:12">
+      <c r="M98" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N98" s="3">
+        <v>8.4</v>
+      </c>
+      <c r="O98" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P98" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16">
       <c r="A99" s="3">
         <v>98</v>
       </c>
@@ -7914,8 +9122,20 @@
       <c r="L99" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="100" spans="1:12">
+      <c r="M99" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N99" s="3">
+        <v>7.9</v>
+      </c>
+      <c r="O99" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P99" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -7952,8 +9172,20 @@
       <c r="L100" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="101" spans="1:12">
+      <c r="M100" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N100" s="3">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -7990,8 +9222,20 @@
       <c r="L101" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="102" spans="1:12">
+      <c r="M101" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N101" s="3">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16">
       <c r="A102" s="3">
         <v>101</v>
       </c>
@@ -8028,8 +9272,20 @@
       <c r="L102" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="103" spans="1:12">
+      <c r="M102" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N102" s="3">
+        <v>7.9</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16">
       <c r="A103" s="3">
         <v>102</v>
       </c>
@@ -8066,8 +9322,20 @@
       <c r="L103" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="104" spans="1:12">
+      <c r="M103" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N103" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="O103" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P103" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -8104,8 +9372,20 @@
       <c r="L104" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="105" spans="1:12">
+      <c r="M104" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N104" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="O104" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P104" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16">
       <c r="A105" s="3">
         <v>104</v>
       </c>
@@ -8142,8 +9422,20 @@
       <c r="L105" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="106" spans="1:12">
+      <c r="M105" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N105" s="3">
+        <v>7.8</v>
+      </c>
+      <c r="O105" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P105" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16">
       <c r="A106" s="3">
         <v>105</v>
       </c>
@@ -8177,8 +9469,20 @@
       <c r="L106" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="107" spans="1:12">
+      <c r="M106" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N106" s="3">
+        <v>6.4</v>
+      </c>
+      <c r="O106" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P106" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -8215,8 +9519,20 @@
       <c r="L107" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="108" spans="1:12">
+      <c r="M107" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N107" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="O107" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P107" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16">
       <c r="A108" s="3">
         <v>107</v>
       </c>
@@ -8253,8 +9569,20 @@
       <c r="L108" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="109" spans="1:12">
+      <c r="M108" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N108" s="3">
+        <v>6.7</v>
+      </c>
+      <c r="O108" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P108" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -8291,8 +9619,20 @@
       <c r="L109" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="110" spans="1:12">
+      <c r="M109" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N109" s="3">
+        <v>8.5</v>
+      </c>
+      <c r="O109" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P109" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -8329,8 +9669,20 @@
       <c r="L110" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="111" spans="1:12">
+      <c r="M110" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N110" s="3">
+        <v>8.9</v>
+      </c>
+      <c r="O110" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P110" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -8367,8 +9719,20 @@
       <c r="L111" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="112" spans="1:12">
+      <c r="M111" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N111" s="3">
+        <v>6.9</v>
+      </c>
+      <c r="O111" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P111" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -8405,8 +9769,20 @@
       <c r="L112" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="113" spans="1:12">
+      <c r="M112" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N112" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="O112" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P112" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -8443,8 +9819,20 @@
       <c r="L113" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="114" spans="1:12">
+      <c r="M113" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N113" s="3">
+        <v>6.8</v>
+      </c>
+      <c r="O113" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P113" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16">
       <c r="A114" s="3">
         <v>113</v>
       </c>
@@ -8481,8 +9869,20 @@
       <c r="L114" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="115" spans="1:12">
+      <c r="M114" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N114" s="3">
+        <v>6.7</v>
+      </c>
+      <c r="O114" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P114" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16">
       <c r="A115" s="3">
         <v>114</v>
       </c>
@@ -8519,8 +9919,20 @@
       <c r="L115" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="116" spans="1:12">
+      <c r="M115" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N115" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="O115" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P115" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16">
       <c r="A116" s="3">
         <v>115</v>
       </c>
@@ -8557,8 +9969,20 @@
       <c r="L116" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="117" spans="1:12">
+      <c r="M116" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N116" s="3">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="O116" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P116" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16">
       <c r="A117" s="3">
         <v>116</v>
       </c>
@@ -8595,8 +10019,20 @@
       <c r="L117" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="118" spans="1:12">
+      <c r="M117" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N117" s="3">
+        <v>9.9</v>
+      </c>
+      <c r="O117" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P117" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16">
       <c r="A118" s="3">
         <v>117</v>
       </c>
@@ -8633,8 +10069,20 @@
       <c r="L118" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="119" spans="1:12">
+      <c r="M118" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N118" s="3">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="O118" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P118" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16">
       <c r="A119" s="3">
         <v>118</v>
       </c>
@@ -8671,8 +10119,20 @@
       <c r="L119" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="120" spans="1:12">
+      <c r="M119" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N119" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="O119" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P119" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16">
       <c r="A120" s="3">
         <v>119</v>
       </c>
@@ -8709,8 +10169,20 @@
       <c r="L120" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="121" spans="1:12">
+      <c r="M120" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N120" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="O120" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P120" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16">
       <c r="A121" s="3">
         <v>120</v>
       </c>
@@ -8747,8 +10219,20 @@
       <c r="L121" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="122" spans="1:12">
+      <c r="M121" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N121" s="3">
+        <v>6</v>
+      </c>
+      <c r="O121" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P121" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16">
       <c r="A122" s="3">
         <v>121</v>
       </c>
@@ -8785,8 +10269,20 @@
       <c r="L122" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="123" spans="1:12">
+      <c r="M122" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N122" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="O122" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P122" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16">
       <c r="A123" s="3">
         <v>122</v>
       </c>
@@ -8823,8 +10319,20 @@
       <c r="L123" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="124" spans="1:12">
+      <c r="M123" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N123" s="3">
+        <v>5.7</v>
+      </c>
+      <c r="O123" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P123" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16">
       <c r="A124" s="3">
         <v>123</v>
       </c>
@@ -8861,8 +10369,20 @@
       <c r="L124" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="125" spans="1:12">
+      <c r="M124" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N124" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="O124" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P124" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16">
       <c r="A125" s="3">
         <v>124</v>
       </c>
@@ -8899,8 +10419,20 @@
       <c r="L125" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="126" spans="1:12">
+      <c r="M125" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N125" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="O125" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P125" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16">
       <c r="A126" s="3">
         <v>125</v>
       </c>
@@ -8937,8 +10469,20 @@
       <c r="L126" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="127" spans="1:12">
+      <c r="M126" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N126" s="3">
+        <v>5</v>
+      </c>
+      <c r="O126" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P126" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16">
       <c r="A127" s="3">
         <v>126</v>
       </c>
@@ -8975,8 +10519,20 @@
       <c r="L127" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="128" spans="1:12">
+      <c r="M127" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N127" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="O127" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P127" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16">
       <c r="A128" s="3">
         <v>127</v>
       </c>
@@ -9013,8 +10569,20 @@
       <c r="L128" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="129" spans="1:12">
+      <c r="M128" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N128" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="O128" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P128" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16">
       <c r="A129" s="3">
         <v>128</v>
       </c>
@@ -9051,8 +10619,20 @@
       <c r="L129" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="130" spans="1:12">
+      <c r="M129" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N129" s="3">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="O129" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P129" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16">
       <c r="A130" s="3">
         <v>129</v>
       </c>
@@ -9089,8 +10669,20 @@
       <c r="L130" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="131" spans="1:12">
+      <c r="M130" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N130" s="3">
+        <v>5.5</v>
+      </c>
+      <c r="O130" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P130" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16">
       <c r="A131" s="3">
         <v>130</v>
       </c>
@@ -9127,8 +10719,20 @@
       <c r="L131" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="132" spans="1:12">
+      <c r="M131" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N131" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="O131" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P131" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16">
       <c r="A132" s="3">
         <v>131</v>
       </c>
@@ -9165,8 +10769,20 @@
       <c r="L132" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="133" spans="1:12">
+      <c r="M132" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N132" s="3">
+        <v>5</v>
+      </c>
+      <c r="O132" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P132" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16">
       <c r="A133" s="3">
         <v>132</v>
       </c>
@@ -9203,8 +10819,20 @@
       <c r="L133" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="134" spans="1:12">
+      <c r="M133" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N133" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="O133" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P133" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16">
       <c r="A134" s="3">
         <v>133</v>
       </c>
@@ -9241,8 +10869,20 @@
       <c r="L134" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="135" spans="1:12">
+      <c r="M134" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N134" s="3">
+        <v>6.7</v>
+      </c>
+      <c r="O134" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P134" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16">
       <c r="A135" s="3">
         <v>134</v>
       </c>
@@ -9279,8 +10919,20 @@
       <c r="L135" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="136" spans="1:12">
+      <c r="M135" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N135" s="3">
+        <v>6</v>
+      </c>
+      <c r="O135" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P135" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16">
       <c r="A136" s="3">
         <v>135</v>
       </c>
@@ -9317,8 +10969,20 @@
       <c r="L136" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="137" spans="1:12">
+      <c r="M136" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N136" s="3">
+        <v>6.8</v>
+      </c>
+      <c r="O136" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P136" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16">
       <c r="A137" s="3">
         <v>136</v>
       </c>
@@ -9355,8 +11019,20 @@
       <c r="L137" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="138" spans="1:12">
+      <c r="M137" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N137" s="3">
+        <v>6.4</v>
+      </c>
+      <c r="O137" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P137" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16">
       <c r="A138" s="3">
         <v>137</v>
       </c>
@@ -9393,8 +11069,20 @@
       <c r="L138" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="139" spans="1:12">
+      <c r="M138" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N138" s="3">
+        <v>5.3</v>
+      </c>
+      <c r="O138" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P138" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16">
       <c r="A139" s="3">
         <v>138</v>
       </c>
@@ -9431,8 +11119,20 @@
       <c r="L139" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="140" spans="1:12">
+      <c r="M139" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N139" s="3">
+        <v>7.8</v>
+      </c>
+      <c r="O139" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P139" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16">
       <c r="A140" s="3">
         <v>139</v>
       </c>
@@ -9469,8 +11169,20 @@
       <c r="L140" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="141" spans="1:12">
+      <c r="M140" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N140" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="O140" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P140" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16">
       <c r="A141" s="3">
         <v>140</v>
       </c>
@@ -9507,8 +11219,20 @@
       <c r="L141" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="142" spans="1:12">
+      <c r="M141" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N141" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="O141" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P141" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16">
       <c r="A142" s="3">
         <v>141</v>
       </c>
@@ -9545,8 +11269,20 @@
       <c r="L142" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="143" spans="1:12">
+      <c r="M142" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N142" s="3">
+        <v>7.7</v>
+      </c>
+      <c r="O142" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P142" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16">
       <c r="A143" s="3">
         <v>142</v>
       </c>
@@ -9583,8 +11319,20 @@
       <c r="L143" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="144" spans="1:12">
+      <c r="M143" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N143" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="O143" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P143" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16">
       <c r="A144" s="3">
         <v>143</v>
       </c>
@@ -9621,8 +11369,20 @@
       <c r="L144" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="145" spans="1:12">
+      <c r="M144" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N144" s="3">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="O144" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P144" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16">
       <c r="A145" s="3">
         <v>144</v>
       </c>
@@ -9659,8 +11419,20 @@
       <c r="L145" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="146" spans="1:12">
+      <c r="M145" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N145" s="3">
+        <v>6.6</v>
+      </c>
+      <c r="O145" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P145" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16">
       <c r="A146" s="3">
         <v>145</v>
       </c>
@@ -9697,8 +11469,20 @@
       <c r="L146" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="147" spans="1:12">
+      <c r="M146" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N146" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="O146" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P146" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16">
       <c r="A147" s="3">
         <v>146</v>
       </c>
@@ -9735,8 +11519,20 @@
       <c r="L147" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="148" spans="1:12">
+      <c r="M147" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N147" s="3">
+        <v>6.3</v>
+      </c>
+      <c r="O147" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P147" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16">
       <c r="A148" s="3">
         <v>147</v>
       </c>
@@ -9773,8 +11569,20 @@
       <c r="L148" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="149" spans="1:12">
+      <c r="M148" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N148" s="3">
+        <v>6.9</v>
+      </c>
+      <c r="O148" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P148" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16">
       <c r="A149" s="3">
         <v>148</v>
       </c>
@@ -9811,8 +11619,20 @@
       <c r="L149" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="150" spans="1:12">
+      <c r="M149" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N149" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="O149" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P149" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16">
       <c r="A150" s="3">
         <v>149</v>
       </c>
@@ -9849,8 +11669,20 @@
       <c r="L150" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="151" spans="1:12">
+      <c r="M150" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N150" s="3">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="O150" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P150" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16">
       <c r="A151" s="3">
         <v>150</v>
       </c>
@@ -9887,8 +11719,20 @@
       <c r="L151" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="152" spans="1:12">
+      <c r="M151" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N151" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="O151" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P151" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16">
       <c r="A152" s="3">
         <v>151</v>
       </c>
@@ -9925,8 +11769,20 @@
       <c r="L152" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="153" spans="1:12">
+      <c r="M152" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N152" s="3">
+        <v>8.4</v>
+      </c>
+      <c r="O152" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P152" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16">
       <c r="A153" s="3">
         <v>152</v>
       </c>
@@ -9963,8 +11819,20 @@
       <c r="L153" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="154" spans="1:12">
+      <c r="M153" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N153" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="O153" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P153" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16">
       <c r="A154" s="3">
         <v>153</v>
       </c>
@@ -10001,8 +11869,20 @@
       <c r="L154" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="155" spans="1:12">
+      <c r="M154" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N154" s="3">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="O154" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P154" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16">
       <c r="A155" s="3">
         <v>154</v>
       </c>
@@ -10039,8 +11919,20 @@
       <c r="L155" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="156" spans="1:12">
+      <c r="M155" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N155" s="3">
+        <v>8.6</v>
+      </c>
+      <c r="O155" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P155" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16">
       <c r="A156" s="3">
         <v>155</v>
       </c>
@@ -10077,8 +11969,20 @@
       <c r="L156" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="157" spans="1:12">
+      <c r="M156" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N156" s="3">
+        <v>8.4</v>
+      </c>
+      <c r="O156" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P156" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16">
       <c r="A157" s="3">
         <v>156</v>
       </c>
@@ -10115,8 +12019,20 @@
       <c r="L157" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="158" spans="1:12">
+      <c r="M157" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N157" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="O157" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P157" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16">
       <c r="A158" s="3">
         <v>157</v>
       </c>
@@ -10153,8 +12069,20 @@
       <c r="L158" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="159" spans="1:12">
+      <c r="M158" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N158" s="3">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="O158" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P158" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16">
       <c r="A159" s="3">
         <v>158</v>
       </c>
@@ -10191,8 +12119,20 @@
       <c r="L159" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="160" spans="1:12">
+      <c r="M159" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N159" s="3">
+        <v>6.8</v>
+      </c>
+      <c r="O159" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P159" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16">
       <c r="A160" s="3">
         <v>159</v>
       </c>
@@ -10229,8 +12169,20 @@
       <c r="L160" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="161" spans="1:12">
+      <c r="M160" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N160" s="3">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="O160" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P160" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16">
       <c r="A161" s="3">
         <v>160</v>
       </c>
@@ -10267,8 +12219,20 @@
       <c r="L161" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="162" spans="1:12">
+      <c r="M161" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N161" s="3">
+        <v>6.7</v>
+      </c>
+      <c r="O161" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P161" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16">
       <c r="A162" s="3">
         <v>161</v>
       </c>
@@ -10305,8 +12269,20 @@
       <c r="L162" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="163" spans="1:12">
+      <c r="M162" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N162" s="3">
+        <v>5.9</v>
+      </c>
+      <c r="O162" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P162" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16">
       <c r="A163" s="3">
         <v>162</v>
       </c>
@@ -10343,8 +12319,20 @@
       <c r="L163" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="164" spans="1:12">
+      <c r="M163" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N163" s="3">
+        <v>5.5</v>
+      </c>
+      <c r="O163" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P163" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16">
       <c r="A164" s="3">
         <v>163</v>
       </c>
@@ -10381,8 +12369,20 @@
       <c r="L164" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="165" spans="1:12">
+      <c r="M164" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N164" s="3">
+        <v>7.9</v>
+      </c>
+      <c r="O164" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P164" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16">
       <c r="A165" s="3">
         <v>164</v>
       </c>
@@ -10419,8 +12419,20 @@
       <c r="L165" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="166" spans="1:12">
+      <c r="M165" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N165" s="3">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="O165" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P165" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16">
       <c r="A166" s="3">
         <v>165</v>
       </c>
@@ -10457,8 +12469,20 @@
       <c r="L166" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="167" spans="1:12">
+      <c r="M166" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N166" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="O166" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P166" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16">
       <c r="A167" s="3">
         <v>166</v>
       </c>
@@ -10495,8 +12519,20 @@
       <c r="L167" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="168" spans="1:12">
+      <c r="M167" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N167" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="O167" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P167" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16">
       <c r="A168" s="3">
         <v>167</v>
       </c>
@@ -10533,8 +12569,20 @@
       <c r="L168" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="169" spans="1:12">
+      <c r="M168" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N168" s="3">
+        <v>6.3</v>
+      </c>
+      <c r="O168" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P168" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16">
       <c r="A169" s="3">
         <v>168</v>
       </c>
@@ -10571,8 +12619,20 @@
       <c r="L169" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="170" spans="1:12">
+      <c r="M169" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N169" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="O169" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P169" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16">
       <c r="A170" s="3">
         <v>169</v>
       </c>
@@ -10609,8 +12669,20 @@
       <c r="L170" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="171" spans="1:12">
+      <c r="M170" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N170" s="3">
+        <v>9.4</v>
+      </c>
+      <c r="O170" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P170" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16">
       <c r="A171" s="3">
         <v>170</v>
       </c>
@@ -10647,8 +12719,20 @@
       <c r="L171" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="172" spans="1:12">
+      <c r="M171" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N171" s="3">
+        <v>5.7</v>
+      </c>
+      <c r="O171" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P171" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16">
       <c r="A172" s="3">
         <v>171</v>
       </c>
@@ -10685,8 +12769,20 @@
       <c r="L172" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="173" spans="1:12">
+      <c r="M172" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N172" s="3">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="O172" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P172" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16">
       <c r="A173" s="3">
         <v>172</v>
       </c>
@@ -10723,8 +12819,20 @@
       <c r="L173" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="174" spans="1:12">
+      <c r="M173" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N173" s="3">
+        <v>8.9</v>
+      </c>
+      <c r="O173" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P173" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16">
       <c r="A174" s="3">
         <v>173</v>
       </c>
@@ -10761,8 +12869,20 @@
       <c r="L174" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="175" spans="1:12">
+      <c r="M174" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N174" s="3">
+        <v>8.4</v>
+      </c>
+      <c r="O174" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P174" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16">
       <c r="A175" s="3">
         <v>174</v>
       </c>
@@ -10799,8 +12919,20 @@
       <c r="L175" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="176" spans="1:12">
+      <c r="M175" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N175" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="O175" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P175" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16">
       <c r="A176" s="3">
         <v>175</v>
       </c>
@@ -10837,8 +12969,20 @@
       <c r="L176" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="177" spans="1:12">
+      <c r="M176" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N176" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="O176" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P176" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16">
       <c r="A177" s="3">
         <v>176</v>
       </c>
@@ -10875,8 +13019,20 @@
       <c r="L177" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="178" spans="1:12">
+      <c r="M177" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N177" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="O177" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P177" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16">
       <c r="A178" s="3">
         <v>177</v>
       </c>
@@ -10913,8 +13069,20 @@
       <c r="L178" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="179" spans="1:12">
+      <c r="M178" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N178" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="O178" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P178" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16">
       <c r="A179" s="3">
         <v>178</v>
       </c>
@@ -10951,8 +13119,20 @@
       <c r="L179" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="180" spans="1:12">
+      <c r="M179" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N179" s="3">
+        <v>6</v>
+      </c>
+      <c r="O179" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P179" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16">
       <c r="A180" s="3">
         <v>179</v>
       </c>
@@ -10989,8 +13169,20 @@
       <c r="L180" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="181" spans="1:12">
+      <c r="M180" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N180" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="O180" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P180" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="181" spans="1:16">
       <c r="A181" s="3">
         <v>180</v>
       </c>
@@ -11027,8 +13219,20 @@
       <c r="L181" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="182" spans="1:12">
+      <c r="M181" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N181" s="3">
+        <v>5.5</v>
+      </c>
+      <c r="O181" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P181" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16">
       <c r="A182" s="3">
         <v>181</v>
       </c>
@@ -11065,8 +13269,20 @@
       <c r="L182" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="183" spans="1:12">
+      <c r="M182" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N182" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="O182" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P182" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="183" spans="1:16">
       <c r="A183" s="3">
         <v>182</v>
       </c>
@@ -11103,8 +13319,20 @@
       <c r="L183" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="184" spans="1:12">
+      <c r="M183" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N183" s="3">
+        <v>5.3</v>
+      </c>
+      <c r="O183" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P183" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16">
       <c r="A184" s="3">
         <v>183</v>
       </c>
@@ -11141,8 +13369,20 @@
       <c r="L184" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="185" spans="1:12">
+      <c r="M184" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N184" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="O184" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P184" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16">
       <c r="A185" s="3">
         <v>184</v>
       </c>
@@ -11179,8 +13419,20 @@
       <c r="L185" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="186" spans="1:12">
+      <c r="M185" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N185" s="3">
+        <v>8</v>
+      </c>
+      <c r="O185" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P185" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16">
       <c r="A186" s="3">
         <v>185</v>
       </c>
@@ -11217,8 +13469,20 @@
       <c r="L186" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="187" spans="1:12">
+      <c r="M186" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N186" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="O186" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P186" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16">
       <c r="A187" s="3">
         <v>186</v>
       </c>
@@ -11255,8 +13519,20 @@
       <c r="L187" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="188" spans="1:12">
+      <c r="M187" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N187" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="O187" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P187" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="188" spans="1:16">
       <c r="A188" s="3">
         <v>187</v>
       </c>
@@ -11293,8 +13569,20 @@
       <c r="L188" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="189" spans="1:12">
+      <c r="M188" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N188" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="O188" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P188" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="189" spans="1:16">
       <c r="A189" s="3">
         <v>188</v>
       </c>
@@ -11331,8 +13619,20 @@
       <c r="L189" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="190" spans="1:12">
+      <c r="M189" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N189" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="O189" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P189" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="190" spans="1:16">
       <c r="A190" s="3">
         <v>189</v>
       </c>
@@ -11369,8 +13669,20 @@
       <c r="L190" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="191" spans="1:12">
+      <c r="M190" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N190" s="3">
+        <v>9</v>
+      </c>
+      <c r="O190" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P190" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16">
       <c r="A191" s="3">
         <v>190</v>
       </c>
@@ -11407,8 +13719,20 @@
       <c r="L191" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="192" spans="1:12">
+      <c r="M191" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N191" s="3">
+        <v>5</v>
+      </c>
+      <c r="O191" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P191" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="192" spans="1:16">
       <c r="A192" s="3">
         <v>191</v>
       </c>
@@ -11445,8 +13769,20 @@
       <c r="L192" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="193" spans="1:12">
+      <c r="M192" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N192" s="3">
+        <v>8.9</v>
+      </c>
+      <c r="O192" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P192" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="193" spans="1:16">
       <c r="A193" s="3">
         <v>192</v>
       </c>
@@ -11483,8 +13819,20 @@
       <c r="L193" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="194" spans="1:12">
+      <c r="M193" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N193" s="3">
+        <v>6</v>
+      </c>
+      <c r="O193" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P193" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="194" spans="1:16">
       <c r="A194" s="3">
         <v>193</v>
       </c>
@@ -11521,8 +13869,20 @@
       <c r="L194" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="195" spans="1:12">
+      <c r="M194" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N194" s="3">
+        <v>5.7</v>
+      </c>
+      <c r="O194" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P194" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="195" spans="1:16">
       <c r="A195" s="3">
         <v>194</v>
       </c>
@@ -11559,8 +13919,20 @@
       <c r="L195" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="196" spans="1:12">
+      <c r="M195" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N195" s="3">
+        <v>5.3</v>
+      </c>
+      <c r="O195" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P195" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="196" spans="1:16">
       <c r="A196" s="3">
         <v>195</v>
       </c>
@@ -11597,8 +13969,20 @@
       <c r="L196" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="197" spans="1:12">
+      <c r="M196" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N196" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="O196" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P196" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16">
       <c r="A197" s="3">
         <v>196</v>
       </c>
@@ -11635,8 +14019,20 @@
       <c r="L197" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="198" spans="1:12">
+      <c r="M197" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N197" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="O197" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P197" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="198" spans="1:16">
       <c r="A198" s="3">
         <v>197</v>
       </c>
@@ -11673,8 +14069,20 @@
       <c r="L198" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="199" spans="1:12">
+      <c r="M198" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N198" s="3">
+        <v>5.7</v>
+      </c>
+      <c r="O198" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P198" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="199" spans="1:16">
       <c r="A199" s="3">
         <v>198</v>
       </c>
@@ -11711,8 +14119,20 @@
       <c r="L199" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="200" spans="1:12">
+      <c r="M199" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N199" s="3">
+        <v>5.9</v>
+      </c>
+      <c r="O199" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P199" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="200" spans="1:16">
       <c r="A200" s="3">
         <v>199</v>
       </c>
@@ -11749,8 +14169,20 @@
       <c r="L200" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="201" spans="1:12">
+      <c r="M200" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N200" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="O200" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P200" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="201" spans="1:16">
       <c r="A201" s="3">
         <v>200</v>
       </c>
@@ -11788,8 +14220,20 @@
       <c r="L201" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="202" spans="1:12">
+      <c r="M201" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N201" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="O201" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P201" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="202" spans="1:16">
       <c r="A202" s="3">
         <v>201</v>
       </c>
@@ -11826,8 +14270,20 @@
       <c r="L202" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="203" spans="1:12">
+      <c r="M202" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N202" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="O202" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P202" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="203" spans="1:16">
       <c r="A203" s="3">
         <v>202</v>
       </c>
@@ -11864,8 +14320,20 @@
       <c r="L203" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="204" spans="1:12">
+      <c r="M203" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N203" s="3">
+        <v>5.5</v>
+      </c>
+      <c r="O203" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P203" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="204" spans="1:16">
       <c r="A204" s="3">
         <v>203</v>
       </c>
@@ -11902,8 +14370,20 @@
       <c r="L204" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="205" spans="1:12">
+      <c r="M204" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N204" s="3">
+        <v>6.3</v>
+      </c>
+      <c r="O204" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P204" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="205" spans="1:16">
       <c r="A205" s="3">
         <v>204</v>
       </c>
@@ -11940,8 +14420,20 @@
       <c r="L205" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="206" spans="1:12">
+      <c r="M205" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N205" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="O205" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P205" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="206" spans="1:16">
       <c r="A206" s="3">
         <v>205</v>
       </c>
@@ -11978,8 +14470,20 @@
       <c r="L206" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="207" spans="1:12">
+      <c r="M206" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N206" s="3">
+        <v>6</v>
+      </c>
+      <c r="O206" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P206" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="207" spans="1:16">
       <c r="A207" s="3">
         <v>206</v>
       </c>
@@ -12016,8 +14520,20 @@
       <c r="L207" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="208" spans="1:12">
+      <c r="M207" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N207" s="3">
+        <v>5.9</v>
+      </c>
+      <c r="O207" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P207" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="208" spans="1:16">
       <c r="A208" s="3">
         <v>207</v>
       </c>
@@ -12054,8 +14570,20 @@
       <c r="L208" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="209" spans="1:12">
+      <c r="M208" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N208" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="O208" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P208" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="209" spans="1:16">
       <c r="A209" s="3">
         <v>208</v>
       </c>
@@ -12092,8 +14620,20 @@
       <c r="L209" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="210" spans="1:12">
+      <c r="M209" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N209" s="3">
+        <v>5.7</v>
+      </c>
+      <c r="O209" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P209" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="210" spans="1:16">
       <c r="A210" s="3">
         <v>209</v>
       </c>
@@ -12130,8 +14670,20 @@
       <c r="L210" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="211" spans="1:12">
+      <c r="M210" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N210" s="3">
+        <v>5.5</v>
+      </c>
+      <c r="O210" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P210" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="211" spans="1:16">
       <c r="A211" s="3">
         <v>210</v>
       </c>
@@ -12168,8 +14720,20 @@
       <c r="L211" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="212" spans="1:12">
+      <c r="M211" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N211" s="3">
+        <v>6.6</v>
+      </c>
+      <c r="O211" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P211" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="212" spans="1:16">
       <c r="A212" s="3">
         <v>211</v>
       </c>
@@ -12206,8 +14770,20 @@
       <c r="L212" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="213" spans="1:12">
+      <c r="M212" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N212" s="3">
+        <v>5.9</v>
+      </c>
+      <c r="O212" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P212" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="213" spans="1:16">
       <c r="A213" s="3">
         <v>212</v>
       </c>
@@ -12244,8 +14820,20 @@
       <c r="L213" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="214" spans="1:12">
+      <c r="M213" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N213" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="O213" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P213" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="214" spans="1:16">
       <c r="A214" s="3">
         <v>213</v>
       </c>
@@ -12282,8 +14870,20 @@
       <c r="L214" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="215" spans="1:12">
+      <c r="M214" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N214" s="3">
+        <v>6.8</v>
+      </c>
+      <c r="O214" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P214" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="215" spans="1:16">
       <c r="A215" s="3">
         <v>214</v>
       </c>
@@ -12320,8 +14920,20 @@
       <c r="L215" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="216" spans="1:12">
+      <c r="M215" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N215" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="O215" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P215" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="216" spans="1:16">
       <c r="A216" s="3">
         <v>215</v>
       </c>
@@ -12358,8 +14970,20 @@
       <c r="L216" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="217" spans="1:12">
+      <c r="M216" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N216" s="3">
+        <v>6.3</v>
+      </c>
+      <c r="O216" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P216" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="217" spans="1:16">
       <c r="A217" s="3">
         <v>216</v>
       </c>
@@ -12396,8 +15020,20 @@
       <c r="L217" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="218" spans="1:12">
+      <c r="M217" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N217" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="O217" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P217" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="218" spans="1:16">
       <c r="A218" s="3">
         <v>217</v>
       </c>
@@ -12434,8 +15070,20 @@
       <c r="L218" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="219" spans="1:12">
+      <c r="M218" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N218" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="O218" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P218" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="219" spans="1:16">
       <c r="A219" s="3">
         <v>218</v>
       </c>
@@ -12472,8 +15120,20 @@
       <c r="L219" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="220" spans="1:12">
+      <c r="M219" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N219" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="O219" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P219" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="220" spans="1:16">
       <c r="A220" s="3">
         <v>219</v>
       </c>
@@ -12507,8 +15167,20 @@
       <c r="L220" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="221" spans="1:12">
+      <c r="M220" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N220" s="3">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="O220" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P220" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="221" spans="1:16">
       <c r="A221" s="3">
         <v>220</v>
       </c>
@@ -12545,8 +15217,20 @@
       <c r="L221" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="222" spans="1:12">
+      <c r="M221" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N221" s="3">
+        <v>5.7</v>
+      </c>
+      <c r="O221" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P221" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="222" spans="1:16">
       <c r="A222" s="3">
         <v>221</v>
       </c>
@@ -12583,8 +15267,20 @@
       <c r="L222" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="223" spans="1:12">
+      <c r="M222" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N222" s="3">
+        <v>9.1</v>
+      </c>
+      <c r="O222" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P222" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="223" spans="1:16">
       <c r="A223" s="3">
         <v>222</v>
       </c>
@@ -12621,8 +15317,20 @@
       <c r="L223" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="224" spans="1:12">
+      <c r="M223" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N223" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="O223" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P223" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="224" spans="1:16">
       <c r="A224" s="3">
         <v>223</v>
       </c>
@@ -12659,8 +15367,20 @@
       <c r="L224" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="225" spans="1:12">
+      <c r="M224" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N224" s="3">
+        <v>5.5</v>
+      </c>
+      <c r="O224" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P224" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="225" spans="1:16">
       <c r="A225" s="3">
         <v>224</v>
       </c>
@@ -12697,8 +15417,20 @@
       <c r="L225" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="226" spans="1:12">
+      <c r="M225" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N225" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="O225" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P225" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="226" spans="1:16">
       <c r="A226" s="3">
         <v>225</v>
       </c>
@@ -12735,8 +15467,20 @@
       <c r="L226" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="227" spans="1:12">
+      <c r="M226" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N226" s="3">
+        <v>5.9</v>
+      </c>
+      <c r="O226" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P226" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="227" spans="1:16">
       <c r="A227" s="3">
         <v>226</v>
       </c>
@@ -12773,8 +15517,20 @@
       <c r="L227" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="228" spans="1:12">
+      <c r="M227" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N227" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="O227" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P227" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="228" spans="1:16">
       <c r="A228" s="3">
         <v>227</v>
       </c>
@@ -12811,8 +15567,20 @@
       <c r="L228" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="229" spans="1:12">
+      <c r="M228" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N228" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="O228" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P228" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="229" spans="1:16">
       <c r="A229" s="3">
         <v>228</v>
       </c>
@@ -12849,8 +15617,20 @@
       <c r="L229" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="230" spans="1:12">
+      <c r="M229" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N229" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="O229" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P229" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="230" spans="1:16">
       <c r="A230" s="3">
         <v>229</v>
       </c>
@@ -12887,8 +15667,20 @@
       <c r="L230" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="231" spans="1:12">
+      <c r="M230" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N230" s="3">
+        <v>5.9</v>
+      </c>
+      <c r="O230" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P230" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="231" spans="1:16">
       <c r="A231" s="3">
         <v>230</v>
       </c>
@@ -12925,8 +15717,20 @@
       <c r="L231" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="232" spans="1:12">
+      <c r="M231" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N231" s="3">
+        <v>5.7</v>
+      </c>
+      <c r="O231" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P231" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="232" spans="1:16">
       <c r="A232" s="3">
         <v>231</v>
       </c>
@@ -12963,8 +15767,20 @@
       <c r="L232" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="233" spans="1:12">
+      <c r="M232" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N232" s="3">
+        <v>5.5</v>
+      </c>
+      <c r="O232" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P232" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="233" spans="1:16">
       <c r="A233" s="3">
         <v>232</v>
       </c>
@@ -13001,8 +15817,20 @@
       <c r="L233" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="234" spans="1:12">
+      <c r="M233" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N233" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="O233" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P233" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="234" spans="1:16">
       <c r="A234" s="3">
         <v>233</v>
       </c>
@@ -13039,8 +15867,20 @@
       <c r="L234" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="235" spans="1:12">
+      <c r="M234" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N234" s="3">
+        <v>6</v>
+      </c>
+      <c r="O234" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P234" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="235" spans="1:16">
       <c r="A235" s="3">
         <v>234</v>
       </c>
@@ -13077,8 +15917,20 @@
       <c r="L235" s="3" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="236" spans="1:12">
+      <c r="M235" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N235" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="O235" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P235" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="236" spans="1:16">
       <c r="A236" s="3">
         <v>235</v>
       </c>
@@ -13115,8 +15967,20 @@
       <c r="L236" s="3" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="237" spans="1:12">
+      <c r="M236" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N236" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="O236" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P236" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="237" spans="1:16">
       <c r="A237" s="3">
         <v>236</v>
       </c>
@@ -13153,8 +16017,20 @@
       <c r="L237" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="238" spans="1:12">
+      <c r="M237" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N237" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="O237" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P237" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="238" spans="1:16">
       <c r="A238" s="3">
         <v>237</v>
       </c>
@@ -13191,8 +16067,20 @@
       <c r="L238" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="239" spans="1:12">
+      <c r="M238" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N238" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="O238" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P238" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="239" spans="1:16">
       <c r="A239" s="3">
         <v>238</v>
       </c>
@@ -13229,8 +16117,20 @@
       <c r="L239" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="240" spans="1:12">
+      <c r="M239" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N239" s="3">
+        <v>6</v>
+      </c>
+      <c r="O239" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P239" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="240" spans="1:16">
       <c r="A240" s="3">
         <v>239</v>
       </c>
@@ -13267,8 +16167,20 @@
       <c r="L240" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="241" spans="1:12">
+      <c r="M240" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N240" s="3">
+        <v>5.7</v>
+      </c>
+      <c r="O240" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P240" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="241" spans="1:16">
       <c r="A241" s="3">
         <v>240</v>
       </c>
@@ -13305,8 +16217,20 @@
       <c r="L241" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="242" spans="1:12">
+      <c r="M241" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N241" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="O241" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P241" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="242" spans="1:16">
       <c r="A242" s="3">
         <v>241</v>
       </c>
@@ -13343,8 +16267,20 @@
       <c r="L242" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="243" spans="1:12">
+      <c r="M242" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N242" s="3">
+        <v>5.5</v>
+      </c>
+      <c r="O242" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P242" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="243" spans="1:16">
       <c r="A243" s="3">
         <v>242</v>
       </c>
@@ -13381,8 +16317,20 @@
       <c r="L243" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="244" spans="1:12">
+      <c r="M243" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N243" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="O243" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P243" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="244" spans="1:16">
       <c r="A244" s="3">
         <v>243</v>
       </c>
@@ -13419,8 +16367,20 @@
       <c r="L244" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="245" spans="1:12">
+      <c r="M244" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N244" s="3">
+        <v>6.3</v>
+      </c>
+      <c r="O244" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P244" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="245" spans="1:16">
       <c r="A245" s="3">
         <v>244</v>
       </c>
@@ -13457,8 +16417,20 @@
       <c r="L245" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="246" spans="1:12">
+      <c r="M245" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N245" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="O245" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P245" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="246" spans="1:16">
       <c r="A246" s="3">
         <v>245</v>
       </c>
@@ -13494,6 +16466,18 @@
       </c>
       <c r="L246" s="3" t="s">
         <v>1082</v>
+      </c>
+      <c r="M246" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N246" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="O246" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P246" s="3" t="s">
+        <v>1095</v>
       </c>
     </row>
   </sheetData>
@@ -13516,8 +16500,9 @@
     <hyperlink ref="G208" r:id="rId16" xr:uid="{B98DD5AC-AAFF-4A78-B850-8FEBF92DE6F2}"/>
     <hyperlink ref="G246" r:id="rId17" xr:uid="{81BBCBE3-54B5-4E9D-AD59-2F33D8D2B688}"/>
     <hyperlink ref="F208" r:id="rId18" xr:uid="{AEF7C1C5-DCAF-4688-AE14-5284AECD4858}"/>
+    <hyperlink ref="F2" r:id="rId19" xr:uid="{B649D9BD-DDFF-4FA8-9ACD-EA2ADC594CE9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId19"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId20"/>
 </worksheet>
 </file>